--- a/jogos_2025-06-27.xlsx
+++ b/jogos_2025-06-27.xlsx
@@ -1039,94 +1039,94 @@
         </is>
       </c>
       <c r="G5" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="H5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I5" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J5" t="n">
         <v>0</v>
       </c>
       <c r="K5" t="inlineStr">
         <is>
-          <t>complete</t>
+          <t>incomplete</t>
         </is>
       </c>
       <c r="L5" t="n">
-        <v>3.15</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>3.44</v>
+        <v>0</v>
       </c>
       <c r="N5" t="n">
-        <v>2.31</v>
+        <v>0</v>
       </c>
       <c r="O5" t="n">
-        <v>3.4</v>
+        <v>0</v>
       </c>
       <c r="P5" t="n">
-        <v>2.08</v>
+        <v>0</v>
       </c>
       <c r="Q5" t="n">
-        <v>2.9</v>
+        <v>0</v>
       </c>
       <c r="R5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="S5" t="n">
-        <v>2.65</v>
+        <v>0</v>
       </c>
       <c r="T5" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="V5" t="n">
-        <v>1.07</v>
+        <v>0</v>
       </c>
       <c r="W5" t="n">
-        <v>1.26</v>
+        <v>0</v>
       </c>
       <c r="X5" t="n">
-        <v>3.5</v>
+        <v>0</v>
       </c>
       <c r="Y5" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="Z5" t="n">
-        <v>1.93</v>
+        <v>0</v>
       </c>
       <c r="AA5" t="n">
-        <v>3.02</v>
+        <v>0</v>
       </c>
       <c r="AB5" t="n">
-        <v>1.35</v>
+        <v>0</v>
       </c>
       <c r="AC5" t="n">
-        <v>1.67</v>
+        <v>0</v>
       </c>
       <c r="AD5" t="n">
-        <v>2.11</v>
+        <v>0</v>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>['30', '79']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>['67']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG5" t="n">
-        <v>1.3</v>
+        <v>0</v>
       </c>
       <c r="AH5" t="n">
-        <v>1.36</v>
+        <v>0</v>
       </c>
       <c r="AI5" t="n">
         <v>0</v>
@@ -1288,25 +1288,25 @@
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>Kokand-1912</t>
+          <t>Nasaf</t>
         </is>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Dinamo Samarqand</t>
+          <t>Pakhtakor</t>
         </is>
       </c>
       <c r="G7" t="n">
         <v>2</v>
       </c>
       <c r="H7" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="I7" t="n">
         <v>1</v>
       </c>
       <c r="J7" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K7" t="inlineStr">
         <is>
@@ -1314,83 +1314,83 @@
         </is>
       </c>
       <c r="L7" t="n">
-        <v>4.5</v>
+        <v>2.2</v>
       </c>
       <c r="M7" t="n">
-        <v>3.8</v>
+        <v>3.05</v>
       </c>
       <c r="N7" t="n">
-        <v>1.7</v>
+        <v>3.21</v>
       </c>
       <c r="O7" t="n">
-        <v>4.8</v>
+        <v>2.85</v>
       </c>
       <c r="P7" t="n">
-        <v>2.26</v>
+        <v>1.93</v>
       </c>
       <c r="Q7" t="n">
-        <v>2.13</v>
+        <v>3.7</v>
       </c>
       <c r="R7" t="n">
-        <v>1.28</v>
+        <v>1.45</v>
       </c>
       <c r="S7" t="n">
-        <v>3.2</v>
+        <v>2.45</v>
       </c>
       <c r="T7" t="n">
-        <v>2.35</v>
+        <v>3.24</v>
       </c>
       <c r="U7" t="n">
-        <v>1.5</v>
+        <v>1.3</v>
       </c>
       <c r="V7" t="n">
-        <v>1.01</v>
+        <v>1.05</v>
       </c>
       <c r="W7" t="n">
-        <v>1.21</v>
+        <v>1.35</v>
       </c>
       <c r="X7" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>2.1</v>
+      </c>
+      <c r="Z7" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA7" t="n">
         <v>4</v>
       </c>
-      <c r="Y7" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="Z7" t="n">
-        <v>2.16</v>
-      </c>
-      <c r="AA7" t="n">
+      <c r="AB7" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="AC7" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AD7" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AE7" t="inlineStr">
+        <is>
+          <t>['29', '62']</t>
+        </is>
+      </c>
+      <c r="AF7" t="inlineStr">
+        <is>
+          <t>['90+4', '90']</t>
+        </is>
+      </c>
+      <c r="AG7" t="n">
+        <v>1.35</v>
+      </c>
+      <c r="AH7" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AI7" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AJ7" t="n">
         <v>2.6</v>
-      </c>
-      <c r="AB7" t="n">
-        <v>1.4</v>
-      </c>
-      <c r="AC7" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AD7" t="n">
-        <v>1.95</v>
-      </c>
-      <c r="AE7" t="inlineStr">
-        <is>
-          <t>['11', '60']</t>
-        </is>
-      </c>
-      <c r="AF7" t="inlineStr">
-        <is>
-          <t>['29', '43', '73']</t>
-        </is>
-      </c>
-      <c r="AG7" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AH7" t="n">
-        <v>1.16</v>
-      </c>
-      <c r="AI7" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="AJ7" t="n">
-        <v>1.53</v>
       </c>
       <c r="AK7" s="3" t="n">
         <v>45835.5</v>
@@ -1407,7 +1407,7 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Uzbekistan Uzbekistan Super League</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
@@ -1417,109 +1417,109 @@
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>Nasaf</t>
+          <t>Auda</t>
         </is>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Pakhtakor</t>
+          <t>Riga</t>
         </is>
       </c>
       <c r="G8" t="n">
+        <v>1</v>
+      </c>
+      <c r="H8" t="n">
+        <v>3</v>
+      </c>
+      <c r="I8" t="n">
+        <v>0</v>
+      </c>
+      <c r="J8" t="n">
         <v>2</v>
       </c>
-      <c r="H8" t="n">
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L8" t="n">
+        <v>9.550000000000001</v>
+      </c>
+      <c r="M8" t="n">
+        <v>4.9</v>
+      </c>
+      <c r="N8" t="n">
+        <v>1.33</v>
+      </c>
+      <c r="O8" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="P8" t="n">
+        <v>2.48</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>1.67</v>
+      </c>
+      <c r="R8" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="S8" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="U8" t="n">
+        <v>1.59</v>
+      </c>
+      <c r="V8" t="n">
+        <v>1.01</v>
+      </c>
+      <c r="W8" t="n">
+        <v>1.18</v>
+      </c>
+      <c r="X8" t="n">
+        <v>4.6</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>1.54</v>
+      </c>
+      <c r="Z8" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AA8" t="n">
+        <v>2.22</v>
+      </c>
+      <c r="AB8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="AC8" t="n">
+        <v>1.75</v>
+      </c>
+      <c r="AD8" t="n">
         <v>2</v>
       </c>
-      <c r="I8" t="n">
-        <v>1</v>
-      </c>
-      <c r="J8" t="n">
-        <v>0</v>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L8" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="M8" t="n">
-        <v>3.05</v>
-      </c>
-      <c r="N8" t="n">
-        <v>3.21</v>
-      </c>
-      <c r="O8" t="n">
-        <v>2.85</v>
-      </c>
-      <c r="P8" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="Q8" t="n">
-        <v>3.7</v>
-      </c>
-      <c r="R8" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="S8" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="T8" t="n">
-        <v>3.24</v>
-      </c>
-      <c r="U8" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="V8" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W8" t="n">
-        <v>1.35</v>
-      </c>
-      <c r="X8" t="n">
-        <v>2.9</v>
-      </c>
-      <c r="Y8" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z8" t="n">
-        <v>1.62</v>
-      </c>
-      <c r="AA8" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB8" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="AC8" t="n">
-        <v>1.8</v>
-      </c>
-      <c r="AD8" t="n">
-        <v>1.85</v>
-      </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>['29', '62']</t>
+          <t>['57']</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>['90+4', '90']</t>
+          <t>['10', '17', '87']</t>
         </is>
       </c>
       <c r="AG8" t="n">
-        <v>1.35</v>
+        <v>1.15</v>
       </c>
       <c r="AH8" t="n">
-        <v>1.6</v>
+        <v>1.08</v>
       </c>
       <c r="AI8" t="n">
-        <v>1.73</v>
+        <v>3</v>
       </c>
       <c r="AJ8" t="n">
-        <v>2.6</v>
+        <v>1.44</v>
       </c>
       <c r="AK8" s="3" t="n">
         <v>45835.5</v>
@@ -1536,7 +1536,7 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Uzbekistan Uzbekistan Super League</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
@@ -1546,22 +1546,22 @@
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>Auda</t>
+          <t>Kokand-1912</t>
         </is>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Riga</t>
+          <t>Dinamo Samarqand</t>
         </is>
       </c>
       <c r="G9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="H9" t="n">
         <v>3</v>
       </c>
       <c r="I9" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J9" t="n">
         <v>2</v>
@@ -1572,83 +1572,83 @@
         </is>
       </c>
       <c r="L9" t="n">
-        <v>9.550000000000001</v>
+        <v>4.5</v>
       </c>
       <c r="M9" t="n">
-        <v>4.9</v>
+        <v>3.8</v>
       </c>
       <c r="N9" t="n">
-        <v>1.33</v>
+        <v>1.7</v>
       </c>
       <c r="O9" t="n">
-        <v>5.5</v>
+        <v>4.8</v>
       </c>
       <c r="P9" t="n">
-        <v>2.48</v>
+        <v>2.26</v>
       </c>
       <c r="Q9" t="n">
-        <v>1.67</v>
+        <v>2.13</v>
       </c>
       <c r="R9" t="n">
-        <v>1.25</v>
+        <v>1.28</v>
       </c>
       <c r="S9" t="n">
-        <v>3.6</v>
+        <v>3.2</v>
       </c>
       <c r="T9" t="n">
-        <v>2.22</v>
+        <v>2.35</v>
       </c>
       <c r="U9" t="n">
-        <v>1.59</v>
+        <v>1.5</v>
       </c>
       <c r="V9" t="n">
         <v>1.01</v>
       </c>
       <c r="W9" t="n">
-        <v>1.18</v>
+        <v>1.21</v>
       </c>
       <c r="X9" t="n">
-        <v>4.6</v>
+        <v>4</v>
       </c>
       <c r="Y9" t="n">
-        <v>1.54</v>
+        <v>1.72</v>
       </c>
       <c r="Z9" t="n">
-        <v>2.25</v>
+        <v>2.16</v>
       </c>
       <c r="AA9" t="n">
-        <v>2.22</v>
+        <v>2.6</v>
       </c>
       <c r="AB9" t="n">
-        <v>1.5</v>
+        <v>1.4</v>
       </c>
       <c r="AC9" t="n">
-        <v>1.75</v>
+        <v>1.62</v>
       </c>
       <c r="AD9" t="n">
-        <v>2</v>
+        <v>1.95</v>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>['57']</t>
+          <t>['11', '60']</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>['10', '17', '87']</t>
+          <t>['29', '43', '73']</t>
         </is>
       </c>
       <c r="AG9" t="n">
-        <v>1.15</v>
+        <v>1.22</v>
       </c>
       <c r="AH9" t="n">
-        <v>1.08</v>
+        <v>1.16</v>
       </c>
       <c r="AI9" t="n">
-        <v>3</v>
+        <v>3.1</v>
       </c>
       <c r="AJ9" t="n">
-        <v>1.44</v>
+        <v>1.53</v>
       </c>
       <c r="AK9" s="3" t="n">
         <v>45835.5</v>
@@ -1665,7 +1665,7 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Belarus Vysheyshaya Liga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
@@ -1675,109 +1675,109 @@
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>Minsk</t>
+          <t>Tallinna FC Levadia</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Slavia</t>
+          <t>Trans</t>
         </is>
       </c>
       <c r="G10" t="n">
         <v>2</v>
       </c>
       <c r="H10" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I10" t="n">
         <v>1</v>
       </c>
       <c r="J10" t="n">
+        <v>0</v>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L10" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="M10" t="n">
+        <v>4.65</v>
+      </c>
+      <c r="N10" t="n">
+        <v>6</v>
+      </c>
+      <c r="O10" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="P10" t="n">
+        <v>2.53</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>5.2</v>
+      </c>
+      <c r="R10" t="n">
+        <v>1.22</v>
+      </c>
+      <c r="S10" t="n">
+        <v>3.6</v>
+      </c>
+      <c r="T10" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="U10" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="V10" t="n">
         <v>1</v>
       </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L10" t="n">
-        <v>4.42</v>
-      </c>
-      <c r="M10" t="n">
-        <v>3.72</v>
-      </c>
-      <c r="N10" t="n">
-        <v>1.77</v>
-      </c>
-      <c r="O10" t="n">
-        <v>5.2</v>
-      </c>
-      <c r="P10" t="n">
-        <v>2.15</v>
-      </c>
-      <c r="Q10" t="n">
-        <v>2.36</v>
-      </c>
-      <c r="R10" t="n">
-        <v>1.41</v>
-      </c>
-      <c r="S10" t="n">
-        <v>2.65</v>
-      </c>
-      <c r="T10" t="n">
-        <v>2.94</v>
-      </c>
-      <c r="U10" t="n">
+      <c r="W10" t="n">
+        <v>1.17</v>
+      </c>
+      <c r="X10" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>2.45</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>2.23</v>
+      </c>
+      <c r="AB10" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="AC10" t="n">
+        <v>1.73</v>
+      </c>
+      <c r="AD10" t="n">
+        <v>2</v>
+      </c>
+      <c r="AE10" t="inlineStr">
+        <is>
+          <t>['9', '90+2']</t>
+        </is>
+      </c>
+      <c r="AF10" t="inlineStr">
+        <is>
+          <t>['83']</t>
+        </is>
+      </c>
+      <c r="AG10" t="n">
+        <v>1.2</v>
+      </c>
+      <c r="AH10" t="n">
+        <v>2.8</v>
+      </c>
+      <c r="AI10" t="n">
         <v>1.4</v>
       </c>
-      <c r="V10" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W10" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="X10" t="n">
+      <c r="AJ10" t="n">
         <v>3.1</v>
-      </c>
-      <c r="Y10" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="Z10" t="n">
-        <v>1.88</v>
-      </c>
-      <c r="AA10" t="n">
-        <v>3.25</v>
-      </c>
-      <c r="AB10" t="n">
-        <v>1.3</v>
-      </c>
-      <c r="AC10" t="n">
-        <v>1.94</v>
-      </c>
-      <c r="AD10" t="n">
-        <v>1.83</v>
-      </c>
-      <c r="AE10" t="inlineStr">
-        <is>
-          <t>['16', '90+5']</t>
-        </is>
-      </c>
-      <c r="AF10" t="inlineStr">
-        <is>
-          <t>['4', '52']</t>
-        </is>
-      </c>
-      <c r="AG10" t="n">
-        <v>2.09</v>
-      </c>
-      <c r="AH10" t="n">
-        <v>1.09</v>
-      </c>
-      <c r="AI10" t="n">
-        <v>0</v>
-      </c>
-      <c r="AJ10" t="n">
-        <v>0</v>
       </c>
       <c r="AK10" s="3" t="n">
         <v>45835.54166666666</v>
@@ -1794,7 +1794,7 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Belarus Vysheyshaya Liga</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
@@ -1804,25 +1804,25 @@
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>Tallinna FC Levadia</t>
+          <t>Minsk</t>
         </is>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Trans</t>
+          <t>Slavia</t>
         </is>
       </c>
       <c r="G11" t="n">
         <v>2</v>
       </c>
       <c r="H11" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="I11" t="n">
         <v>1</v>
       </c>
       <c r="J11" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K11" t="inlineStr">
         <is>
@@ -1830,83 +1830,83 @@
         </is>
       </c>
       <c r="L11" t="n">
-        <v>1.4</v>
+        <v>5.3</v>
       </c>
       <c r="M11" t="n">
-        <v>4.65</v>
+        <v>3.61</v>
       </c>
       <c r="N11" t="n">
-        <v>6</v>
+        <v>1.57</v>
       </c>
       <c r="O11" t="n">
-        <v>1.88</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>2.53</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>5.2</v>
+        <v>0</v>
       </c>
       <c r="R11" t="n">
-        <v>1.22</v>
+        <v>0</v>
       </c>
       <c r="S11" t="n">
-        <v>3.6</v>
+        <v>0</v>
       </c>
       <c r="T11" t="n">
-        <v>2.2</v>
+        <v>0</v>
       </c>
       <c r="U11" t="n">
-        <v>1.62</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="W11" t="n">
-        <v>1.17</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>4.75</v>
+        <v>0</v>
       </c>
       <c r="Y11" t="n">
-        <v>1.5</v>
+        <v>2</v>
       </c>
       <c r="Z11" t="n">
-        <v>2.45</v>
+        <v>1.72</v>
       </c>
       <c r="AA11" t="n">
-        <v>2.23</v>
+        <v>0</v>
       </c>
       <c r="AB11" t="n">
-        <v>1.6</v>
+        <v>0</v>
       </c>
       <c r="AC11" t="n">
-        <v>1.73</v>
+        <v>0</v>
       </c>
       <c r="AD11" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>['9', '90+2']</t>
+          <t>['16', '9005']</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>['83']</t>
+          <t>['4', '52']</t>
         </is>
       </c>
       <c r="AG11" t="n">
-        <v>1.2</v>
+        <v>0</v>
       </c>
       <c r="AH11" t="n">
-        <v>2.8</v>
+        <v>0</v>
       </c>
       <c r="AI11" t="n">
-        <v>1.4</v>
+        <v>0</v>
       </c>
       <c r="AJ11" t="n">
-        <v>3.1</v>
+        <v>0</v>
       </c>
       <c r="AK11" s="3" t="n">
         <v>45835.54166666666</v>
@@ -1959,58 +1959,58 @@
         </is>
       </c>
       <c r="L12" t="n">
-        <v>1.57</v>
+        <v>1.69</v>
       </c>
       <c r="M12" t="n">
-        <v>4</v>
+        <v>3.66</v>
       </c>
       <c r="N12" t="n">
-        <v>5</v>
+        <v>3.91</v>
       </c>
       <c r="O12" t="n">
-        <v>2.07</v>
+        <v>2.2</v>
       </c>
       <c r="P12" t="n">
-        <v>2.34</v>
+        <v>2.25</v>
       </c>
       <c r="Q12" t="n">
-        <v>5</v>
+        <v>4.5</v>
       </c>
       <c r="R12" t="n">
-        <v>1.3</v>
+        <v>1.33</v>
       </c>
       <c r="S12" t="n">
-        <v>3.2</v>
+        <v>3</v>
       </c>
       <c r="T12" t="n">
-        <v>2.3</v>
+        <v>2.45</v>
       </c>
       <c r="U12" t="n">
-        <v>1.5</v>
+        <v>1.48</v>
       </c>
       <c r="V12" t="n">
-        <v>1.04</v>
+        <v>1.05</v>
       </c>
       <c r="W12" t="n">
-        <v>1.17</v>
+        <v>1.25</v>
       </c>
       <c r="X12" t="n">
-        <v>4.3</v>
+        <v>3.85</v>
       </c>
       <c r="Y12" t="n">
+        <v>1.76</v>
+      </c>
+      <c r="Z12" t="n">
+        <v>1.94</v>
+      </c>
+      <c r="AA12" t="n">
+        <v>3</v>
+      </c>
+      <c r="AB12" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC12" t="n">
         <v>1.7</v>
-      </c>
-      <c r="Z12" t="n">
-        <v>2.1</v>
-      </c>
-      <c r="AA12" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB12" t="n">
-        <v>1.45</v>
-      </c>
-      <c r="AC12" t="n">
-        <v>1.75</v>
       </c>
       <c r="AD12" t="n">
         <v>2</v>
@@ -2026,16 +2026,16 @@
         </is>
       </c>
       <c r="AG12" t="n">
-        <v>1.22</v>
+        <v>1.18</v>
       </c>
       <c r="AH12" t="n">
-        <v>2.3</v>
+        <v>2.05</v>
       </c>
       <c r="AI12" t="n">
-        <v>0</v>
+        <v>1.57</v>
       </c>
       <c r="AJ12" t="n">
-        <v>0</v>
+        <v>2.75</v>
       </c>
       <c r="AK12" s="3" t="n">
         <v>45835.58333333334</v>
@@ -2071,13 +2071,13 @@
         </is>
       </c>
       <c r="G13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H13" t="n">
         <v>2</v>
       </c>
       <c r="I13" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J13" t="n">
         <v>1</v>
@@ -2088,22 +2088,22 @@
         </is>
       </c>
       <c r="L13" t="n">
-        <v>2.13</v>
+        <v>2.4</v>
       </c>
       <c r="M13" t="n">
-        <v>3.31</v>
+        <v>3.25</v>
       </c>
       <c r="N13" t="n">
-        <v>2.88</v>
+        <v>2.5</v>
       </c>
       <c r="O13" t="n">
-        <v>2.85</v>
+        <v>3.15</v>
       </c>
       <c r="P13" t="n">
-        <v>2.15</v>
+        <v>2.25</v>
       </c>
       <c r="Q13" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="R13" t="n">
         <v>1.33</v>
@@ -2112,16 +2112,16 @@
         <v>3</v>
       </c>
       <c r="T13" t="n">
-        <v>2.45</v>
+        <v>2.5</v>
       </c>
       <c r="U13" t="n">
-        <v>1.48</v>
+        <v>1.5</v>
       </c>
       <c r="V13" t="n">
-        <v>1.05</v>
+        <v>1.02</v>
       </c>
       <c r="W13" t="n">
-        <v>1.25</v>
+        <v>1.22</v>
       </c>
       <c r="X13" t="n">
         <v>4</v>
@@ -2130,23 +2130,23 @@
         <v>1.76</v>
       </c>
       <c r="Z13" t="n">
-        <v>1.94</v>
+        <v>2.1</v>
       </c>
       <c r="AA13" t="n">
-        <v>2.8</v>
+        <v>2.62</v>
       </c>
       <c r="AB13" t="n">
-        <v>1.44</v>
+        <v>1.4</v>
       </c>
       <c r="AC13" t="n">
-        <v>1.55</v>
+        <v>1.57</v>
       </c>
       <c r="AD13" t="n">
         <v>2.25</v>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['45+1']</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -2155,16 +2155,16 @@
         </is>
       </c>
       <c r="AG13" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AH13" t="n">
-        <v>1.57</v>
+        <v>1.51</v>
       </c>
       <c r="AI13" t="n">
-        <v>1.9</v>
+        <v>0</v>
       </c>
       <c r="AJ13" t="n">
-        <v>2.1</v>
+        <v>0</v>
       </c>
       <c r="AK13" s="3" t="n">
         <v>45835.58333333334</v>
@@ -2181,7 +2181,7 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>Estonia Meistriliiga</t>
+          <t>Latvia Virsliga</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
@@ -2191,25 +2191,25 @@
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>Vaprus</t>
+          <t>Super Nova</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Nõmme Kalju</t>
+          <t>Metta - LU</t>
         </is>
       </c>
       <c r="G14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="H14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="I14" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J14" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="K14" t="inlineStr">
         <is>
@@ -2217,83 +2217,83 @@
         </is>
       </c>
       <c r="L14" t="n">
-        <v>5.5</v>
+        <v>1.55</v>
       </c>
       <c r="M14" t="n">
-        <v>4.3</v>
+        <v>3.8</v>
       </c>
       <c r="N14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="O14" t="n">
+        <v>2.21</v>
+      </c>
+      <c r="P14" t="n">
+        <v>2.19</v>
+      </c>
+      <c r="Q14" t="n">
+        <v>4.75</v>
+      </c>
+      <c r="R14" t="n">
+        <v>1.38</v>
+      </c>
+      <c r="S14" t="n">
+        <v>3</v>
+      </c>
+      <c r="T14" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="U14" t="n">
         <v>1.44</v>
       </c>
-      <c r="O14" t="n">
-        <v>5.6</v>
-      </c>
-      <c r="P14" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Q14" t="n">
-        <v>1.92</v>
-      </c>
-      <c r="R14" t="n">
-        <v>1.29</v>
-      </c>
-      <c r="S14" t="n">
+      <c r="V14" t="n">
+        <v>1.05</v>
+      </c>
+      <c r="W14" t="n">
+        <v>1.25</v>
+      </c>
+      <c r="X14" t="n">
         <v>3.5</v>
       </c>
-      <c r="T14" t="n">
+      <c r="Y14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="Z14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AA14" t="n">
+        <v>3.2</v>
+      </c>
+      <c r="AB14" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="AC14" t="n">
+        <v>1.85</v>
+      </c>
+      <c r="AD14" t="n">
+        <v>1.88</v>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>['55']</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
+          <t>['68']</t>
+        </is>
+      </c>
+      <c r="AG14" t="n">
+        <v>1.14</v>
+      </c>
+      <c r="AH14" t="n">
         <v>2.3</v>
       </c>
-      <c r="U14" t="n">
-        <v>1.53</v>
-      </c>
-      <c r="V14" t="n">
-        <v>1.01</v>
-      </c>
-      <c r="W14" t="n">
-        <v>1.12</v>
-      </c>
-      <c r="X14" t="n">
-        <v>4.4</v>
-      </c>
-      <c r="Y14" t="n">
-        <v>1.66</v>
-      </c>
-      <c r="Z14" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="AA14" t="n">
-        <v>2.59</v>
-      </c>
-      <c r="AB14" t="n">
+      <c r="AI14" t="n">
         <v>1.44</v>
       </c>
-      <c r="AC14" t="n">
-        <v>1.72</v>
-      </c>
-      <c r="AD14" t="n">
-        <v>2.05</v>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>['14', '58']</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>['8', '27']</t>
-        </is>
-      </c>
-      <c r="AG14" t="n">
-        <v>1.2</v>
-      </c>
-      <c r="AH14" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="AI14" t="n">
-        <v>3.1</v>
-      </c>
       <c r="AJ14" t="n">
-        <v>1.4</v>
+        <v>3</v>
       </c>
       <c r="AK14" s="3" t="n">
         <v>45835.58333333334</v>
@@ -2310,7 +2310,7 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Latvia Virsliga</t>
+          <t>Finland Veikkausliiga</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
@@ -2320,22 +2320,22 @@
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>Super Nova</t>
+          <t>KuPS</t>
         </is>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Metta - LU</t>
+          <t>HJK</t>
         </is>
       </c>
       <c r="G15" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H15" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I15" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J15" t="n">
         <v>0</v>
@@ -2346,83 +2346,83 @@
         </is>
       </c>
       <c r="L15" t="n">
-        <v>1.55</v>
+        <v>2.59</v>
       </c>
       <c r="M15" t="n">
-        <v>3.8</v>
+        <v>3.58</v>
       </c>
       <c r="N15" t="n">
-        <v>4.75</v>
+        <v>2.57</v>
       </c>
       <c r="O15" t="n">
-        <v>2.21</v>
+        <v>2.98</v>
       </c>
       <c r="P15" t="n">
-        <v>2.19</v>
+        <v>2.25</v>
       </c>
       <c r="Q15" t="n">
-        <v>4.75</v>
+        <v>2.93</v>
       </c>
       <c r="R15" t="n">
-        <v>1.38</v>
+        <v>1.27</v>
       </c>
       <c r="S15" t="n">
-        <v>3</v>
+        <v>3.4</v>
       </c>
       <c r="T15" t="n">
-        <v>2.62</v>
+        <v>2.44</v>
       </c>
       <c r="U15" t="n">
+        <v>1.6</v>
+      </c>
+      <c r="V15" t="n">
+        <v>1.03</v>
+      </c>
+      <c r="W15" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="X15" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="Y15" t="n">
+        <v>1.63</v>
+      </c>
+      <c r="Z15" t="n">
+        <v>2.2</v>
+      </c>
+      <c r="AA15" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB15" t="n">
         <v>1.44</v>
       </c>
-      <c r="V15" t="n">
-        <v>1.05</v>
-      </c>
-      <c r="W15" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="X15" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="Y15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="Z15" t="n">
-        <v>1.85</v>
-      </c>
-      <c r="AA15" t="n">
-        <v>3.2</v>
-      </c>
-      <c r="AB15" t="n">
-        <v>1.3</v>
-      </c>
       <c r="AC15" t="n">
-        <v>1.85</v>
+        <v>1.53</v>
       </c>
       <c r="AD15" t="n">
-        <v>1.88</v>
+        <v>2.4</v>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>['55']</t>
+          <t>['2', '8', '71']</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>['68']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG15" t="n">
-        <v>1.14</v>
+        <v>1.5</v>
       </c>
       <c r="AH15" t="n">
-        <v>2.3</v>
+        <v>1.53</v>
       </c>
       <c r="AI15" t="n">
-        <v>1.44</v>
+        <v>2.2</v>
       </c>
       <c r="AJ15" t="n">
-        <v>3</v>
+        <v>1.73</v>
       </c>
       <c r="AK15" s="3" t="n">
         <v>45835.58333333334</v>
@@ -2439,7 +2439,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Finland Veikkausliiga</t>
+          <t>Estonia Meistriliiga</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
@@ -2449,109 +2449,109 @@
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>KuPS</t>
+          <t>Vaprus</t>
         </is>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>HJK</t>
+          <t>Nõmme Kalju</t>
         </is>
       </c>
       <c r="G16" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="H16" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="I16" t="n">
+        <v>1</v>
+      </c>
+      <c r="J16" t="n">
         <v>2</v>
       </c>
-      <c r="J16" t="n">
-        <v>0</v>
-      </c>
       <c r="K16" t="inlineStr">
         <is>
           <t>complete</t>
         </is>
       </c>
       <c r="L16" t="n">
-        <v>2.59</v>
+        <v>5.5</v>
       </c>
       <c r="M16" t="n">
-        <v>3.58</v>
+        <v>4.3</v>
       </c>
       <c r="N16" t="n">
-        <v>2.57</v>
+        <v>1.44</v>
       </c>
       <c r="O16" t="n">
-        <v>2.98</v>
+        <v>5.6</v>
       </c>
       <c r="P16" t="n">
-        <v>2.25</v>
+        <v>2.5</v>
       </c>
       <c r="Q16" t="n">
-        <v>2.93</v>
+        <v>1.92</v>
       </c>
       <c r="R16" t="n">
-        <v>1.27</v>
+        <v>1.29</v>
       </c>
       <c r="S16" t="n">
-        <v>3.4</v>
+        <v>3.5</v>
       </c>
       <c r="T16" t="n">
-        <v>2.44</v>
+        <v>2.3</v>
       </c>
       <c r="U16" t="n">
-        <v>1.6</v>
+        <v>1.53</v>
       </c>
       <c r="V16" t="n">
-        <v>1.03</v>
+        <v>1.01</v>
       </c>
       <c r="W16" t="n">
-        <v>1.15</v>
+        <v>1.12</v>
       </c>
       <c r="X16" t="n">
-        <v>4.5</v>
+        <v>4.4</v>
       </c>
       <c r="Y16" t="n">
-        <v>1.63</v>
+        <v>1.66</v>
       </c>
       <c r="Z16" t="n">
         <v>2.2</v>
       </c>
       <c r="AA16" t="n">
-        <v>2.5</v>
+        <v>2.59</v>
       </c>
       <c r="AB16" t="n">
         <v>1.44</v>
       </c>
       <c r="AC16" t="n">
-        <v>1.53</v>
+        <v>1.72</v>
       </c>
       <c r="AD16" t="n">
-        <v>2.4</v>
+        <v>2.05</v>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>['2', '8', '71']</t>
+          <t>['14', '58']</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['8', '27']</t>
         </is>
       </c>
       <c r="AG16" t="n">
-        <v>1.5</v>
+        <v>1.2</v>
       </c>
       <c r="AH16" t="n">
-        <v>1.53</v>
+        <v>1.06</v>
       </c>
       <c r="AI16" t="n">
-        <v>2.2</v>
+        <v>3.1</v>
       </c>
       <c r="AJ16" t="n">
-        <v>1.73</v>
+        <v>1.4</v>
       </c>
       <c r="AK16" s="3" t="n">
         <v>45835.58333333334</v>
@@ -2826,7 +2826,7 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Republic of Ireland Premier Division</t>
+          <t>Republic of Ireland First Division</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
@@ -2836,25 +2836,25 @@
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>Galway United</t>
+          <t>Athlone Town</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Shelbourne</t>
+          <t>Bray Wanderers</t>
         </is>
       </c>
       <c r="G19" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="H19" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="I19" t="n">
         <v>0</v>
       </c>
       <c r="J19" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="K19" t="inlineStr">
         <is>
@@ -2862,83 +2862,83 @@
         </is>
       </c>
       <c r="L19" t="n">
-        <v>2.83</v>
+        <v>2.87</v>
       </c>
       <c r="M19" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="N19" t="n">
-        <v>2.55</v>
+        <v>2.25</v>
       </c>
       <c r="O19" t="n">
-        <v>3.82</v>
+        <v>3.4</v>
       </c>
       <c r="P19" t="n">
-        <v>1.93</v>
+        <v>2.2</v>
       </c>
       <c r="Q19" t="n">
-        <v>3.15</v>
+        <v>2.75</v>
       </c>
       <c r="R19" t="n">
-        <v>1.51</v>
+        <v>1.32</v>
       </c>
       <c r="S19" t="n">
-        <v>2.62</v>
+        <v>3.1</v>
       </c>
       <c r="T19" t="n">
-        <v>3.28</v>
+        <v>2.45</v>
       </c>
       <c r="U19" t="n">
-        <v>1.3</v>
+        <v>1.49</v>
       </c>
       <c r="V19" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W19" t="n">
-        <v>1.45</v>
+        <v>1.22</v>
       </c>
       <c r="X19" t="n">
-        <v>2.7</v>
+        <v>4.1</v>
       </c>
       <c r="Y19" t="n">
-        <v>2.38</v>
+        <v>1.83</v>
       </c>
       <c r="Z19" t="n">
+        <v>2.03</v>
+      </c>
+      <c r="AA19" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="AB19" t="n">
+        <v>1.42</v>
+      </c>
+      <c r="AC19" t="n">
         <v>1.62</v>
       </c>
-      <c r="AA19" t="n">
-        <v>4</v>
-      </c>
-      <c r="AB19" t="n">
-        <v>1.21</v>
-      </c>
-      <c r="AC19" t="n">
-        <v>1.83</v>
-      </c>
       <c r="AD19" t="n">
-        <v>1.85</v>
+        <v>2.2</v>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>['84']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>['25']</t>
+          <t>['30', '21', '53', '66']</t>
         </is>
       </c>
       <c r="AG19" t="n">
-        <v>1.35</v>
+        <v>1.25</v>
       </c>
       <c r="AH19" t="n">
-        <v>1.37</v>
+        <v>1.41</v>
       </c>
       <c r="AI19" t="n">
-        <v>2.1</v>
+        <v>2.2</v>
       </c>
       <c r="AJ19" t="n">
-        <v>2.15</v>
+        <v>1.73</v>
       </c>
       <c r="AK19" s="3" t="n">
         <v>45835.65625</v>
@@ -2955,7 +2955,7 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>Republic of Ireland First Division</t>
+          <t>Republic of Ireland Premier Division</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
@@ -2965,109 +2965,109 @@
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>Athlone Town</t>
+          <t>Galway United</t>
         </is>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bray Wanderers</t>
+          <t>Shelbourne</t>
         </is>
       </c>
       <c r="G20" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H20" t="n">
+        <v>1</v>
+      </c>
+      <c r="I20" t="n">
+        <v>0</v>
+      </c>
+      <c r="J20" t="n">
+        <v>1</v>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>complete</t>
+        </is>
+      </c>
+      <c r="L20" t="n">
+        <v>2.83</v>
+      </c>
+      <c r="M20" t="n">
+        <v>2.9</v>
+      </c>
+      <c r="N20" t="n">
+        <v>2.55</v>
+      </c>
+      <c r="O20" t="n">
+        <v>3.82</v>
+      </c>
+      <c r="P20" t="n">
+        <v>1.93</v>
+      </c>
+      <c r="Q20" t="n">
+        <v>3.15</v>
+      </c>
+      <c r="R20" t="n">
+        <v>1.51</v>
+      </c>
+      <c r="S20" t="n">
+        <v>2.62</v>
+      </c>
+      <c r="T20" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="U20" t="n">
+        <v>1.3</v>
+      </c>
+      <c r="V20" t="n">
+        <v>1.06</v>
+      </c>
+      <c r="W20" t="n">
+        <v>1.45</v>
+      </c>
+      <c r="X20" t="n">
+        <v>2.7</v>
+      </c>
+      <c r="Y20" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="Z20" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AA20" t="n">
         <v>4</v>
       </c>
-      <c r="I20" t="n">
-        <v>0</v>
-      </c>
-      <c r="J20" t="n">
-        <v>2</v>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>complete</t>
-        </is>
-      </c>
-      <c r="L20" t="n">
-        <v>2.87</v>
-      </c>
-      <c r="M20" t="n">
-        <v>3.3</v>
-      </c>
-      <c r="N20" t="n">
-        <v>2.25</v>
-      </c>
-      <c r="O20" t="n">
-        <v>3.4</v>
-      </c>
-      <c r="P20" t="n">
-        <v>2.2</v>
-      </c>
-      <c r="Q20" t="n">
-        <v>2.75</v>
-      </c>
-      <c r="R20" t="n">
-        <v>1.32</v>
-      </c>
-      <c r="S20" t="n">
-        <v>3.1</v>
-      </c>
-      <c r="T20" t="n">
-        <v>2.45</v>
-      </c>
-      <c r="U20" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="V20" t="n">
-        <v>1.04</v>
-      </c>
-      <c r="W20" t="n">
-        <v>1.22</v>
-      </c>
-      <c r="X20" t="n">
-        <v>4.1</v>
-      </c>
-      <c r="Y20" t="n">
+      <c r="AB20" t="n">
+        <v>1.21</v>
+      </c>
+      <c r="AC20" t="n">
         <v>1.83</v>
       </c>
-      <c r="Z20" t="n">
-        <v>2.03</v>
-      </c>
-      <c r="AA20" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="AB20" t="n">
-        <v>1.42</v>
-      </c>
-      <c r="AC20" t="n">
-        <v>1.62</v>
-      </c>
       <c r="AD20" t="n">
-        <v>2.2</v>
+        <v>1.85</v>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['84']</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>['30', '21', '53', '66']</t>
+          <t>['25']</t>
         </is>
       </c>
       <c r="AG20" t="n">
-        <v>1.25</v>
+        <v>1.35</v>
       </c>
       <c r="AH20" t="n">
-        <v>1.41</v>
+        <v>1.37</v>
       </c>
       <c r="AI20" t="n">
-        <v>2.2</v>
+        <v>2.1</v>
       </c>
       <c r="AJ20" t="n">
-        <v>1.73</v>
+        <v>2.15</v>
       </c>
       <c r="AK20" s="3" t="n">
         <v>45835.65625</v>
@@ -3094,22 +3094,22 @@
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>Dundalk</t>
+          <t>Treaty United</t>
         </is>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Cobh Ramblers</t>
+          <t>Finn Harps</t>
         </is>
       </c>
       <c r="G21" t="n">
+        <v>0</v>
+      </c>
+      <c r="H21" t="n">
         <v>1</v>
       </c>
-      <c r="H21" t="n">
-        <v>0</v>
-      </c>
       <c r="I21" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J21" t="n">
         <v>0</v>
@@ -3120,83 +3120,83 @@
         </is>
       </c>
       <c r="L21" t="n">
-        <v>2.2</v>
+        <v>1.5</v>
       </c>
       <c r="M21" t="n">
-        <v>3.15</v>
+        <v>3.95</v>
       </c>
       <c r="N21" t="n">
-        <v>3.1</v>
+        <v>3.82</v>
       </c>
       <c r="O21" t="n">
-        <v>2.75</v>
+        <v>2.38</v>
       </c>
       <c r="P21" t="n">
-        <v>2.11</v>
+        <v>2.3</v>
       </c>
       <c r="Q21" t="n">
-        <v>3.9</v>
+        <v>4.1</v>
       </c>
       <c r="R21" t="n">
-        <v>1.36</v>
+        <v>1.3</v>
       </c>
       <c r="S21" t="n">
-        <v>2.8</v>
+        <v>3.05</v>
       </c>
       <c r="T21" t="n">
-        <v>2.8</v>
+        <v>2.48</v>
       </c>
       <c r="U21" t="n">
-        <v>1.37</v>
+        <v>1.47</v>
       </c>
       <c r="V21" t="n">
-        <v>1.06</v>
+        <v>1.04</v>
       </c>
       <c r="W21" t="n">
-        <v>1.31</v>
+        <v>1.2</v>
       </c>
       <c r="X21" t="n">
-        <v>3.35</v>
+        <v>3.95</v>
       </c>
       <c r="Y21" t="n">
-        <v>2.12</v>
+        <v>1.68</v>
       </c>
       <c r="Z21" t="n">
-        <v>1.74</v>
+        <v>2.05</v>
       </c>
       <c r="AA21" t="n">
-        <v>3.6</v>
+        <v>2.5</v>
       </c>
       <c r="AB21" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="AC21" t="n">
+        <v>1.62</v>
+      </c>
+      <c r="AD21" t="n">
+        <v>2.25</v>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>[]</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>['75']</t>
+        </is>
+      </c>
+      <c r="AG21" t="n">
         <v>1.25</v>
       </c>
-      <c r="AC21" t="n">
-        <v>1.81</v>
-      </c>
-      <c r="AD21" t="n">
-        <v>1.93</v>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>['13']</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="AG21" t="n">
-        <v>1.37</v>
-      </c>
       <c r="AH21" t="n">
-        <v>1.68</v>
+        <v>1.97</v>
       </c>
       <c r="AI21" t="n">
-        <v>1.62</v>
+        <v>1.46</v>
       </c>
       <c r="AJ21" t="n">
-        <v>2.62</v>
+        <v>2.73</v>
       </c>
       <c r="AK21" s="3" t="n">
         <v>45835.65625</v>
@@ -3223,25 +3223,25 @@
       </c>
       <c r="E22" t="inlineStr">
         <is>
-          <t>Cork City</t>
+          <t>Bohemians</t>
         </is>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>St Patrick's Athl.</t>
+          <t>Sligo Rovers</t>
         </is>
       </c>
       <c r="G22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I22" t="n">
         <v>0</v>
       </c>
       <c r="J22" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K22" t="inlineStr">
         <is>
@@ -3249,83 +3249,83 @@
         </is>
       </c>
       <c r="L22" t="n">
-        <v>3.8</v>
+        <v>1.33</v>
       </c>
       <c r="M22" t="n">
-        <v>3.35</v>
+        <v>4.93</v>
       </c>
       <c r="N22" t="n">
-        <v>1.9</v>
+        <v>8</v>
       </c>
       <c r="O22" t="n">
-        <v>4.57</v>
+        <v>1.86</v>
       </c>
       <c r="P22" t="n">
-        <v>2.26</v>
+        <v>2.71</v>
       </c>
       <c r="Q22" t="n">
-        <v>2.61</v>
+        <v>5.3</v>
       </c>
       <c r="R22" t="n">
-        <v>1.37</v>
+        <v>1.25</v>
       </c>
       <c r="S22" t="n">
-        <v>2.98</v>
+        <v>3.5</v>
       </c>
       <c r="T22" t="n">
-        <v>3.02</v>
+        <v>2.35</v>
       </c>
       <c r="U22" t="n">
-        <v>1.4</v>
+        <v>1.6</v>
       </c>
       <c r="V22" t="n">
         <v>1.02</v>
       </c>
       <c r="W22" t="n">
-        <v>1.32</v>
+        <v>1.17</v>
       </c>
       <c r="X22" t="n">
-        <v>3.47</v>
+        <v>4.72</v>
       </c>
       <c r="Y22" t="n">
-        <v>2.04</v>
+        <v>1.64</v>
       </c>
       <c r="Z22" t="n">
-        <v>1.84</v>
+        <v>2.32</v>
       </c>
       <c r="AA22" t="n">
-        <v>3.55</v>
+        <v>2.62</v>
       </c>
       <c r="AB22" t="n">
-        <v>1.31</v>
+        <v>1.52</v>
       </c>
       <c r="AC22" t="n">
-        <v>1.87</v>
+        <v>1.8</v>
       </c>
       <c r="AD22" t="n">
-        <v>1.87</v>
+        <v>1.85</v>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['90+5']</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['28']</t>
         </is>
       </c>
       <c r="AG22" t="n">
-        <v>1.27</v>
+        <v>1.13</v>
       </c>
       <c r="AH22" t="n">
-        <v>1.18</v>
+        <v>3.3</v>
       </c>
       <c r="AI22" t="n">
-        <v>2.62</v>
+        <v>1.4</v>
       </c>
       <c r="AJ22" t="n">
-        <v>1.67</v>
+        <v>3.3</v>
       </c>
       <c r="AK22" s="3" t="n">
         <v>45835.65625</v>
@@ -3352,22 +3352,22 @@
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>Derry City</t>
+          <t>Cork City</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Drogheda United</t>
+          <t>St Patrick's Athl.</t>
         </is>
       </c>
       <c r="G23" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="H23" t="n">
         <v>0</v>
       </c>
       <c r="I23" t="n">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
         <v>0</v>
@@ -3378,65 +3378,65 @@
         </is>
       </c>
       <c r="L23" t="n">
-        <v>1.6</v>
+        <v>3.8</v>
       </c>
       <c r="M23" t="n">
-        <v>3.1</v>
+        <v>3.35</v>
       </c>
       <c r="N23" t="n">
-        <v>5.73</v>
+        <v>1.9</v>
       </c>
       <c r="O23" t="n">
-        <v>2.52</v>
+        <v>4.57</v>
       </c>
       <c r="P23" t="n">
-        <v>2.02</v>
+        <v>2.26</v>
       </c>
       <c r="Q23" t="n">
-        <v>6.43</v>
+        <v>2.61</v>
       </c>
       <c r="R23" t="n">
-        <v>1.55</v>
+        <v>1.37</v>
       </c>
       <c r="S23" t="n">
-        <v>2.38</v>
+        <v>2.98</v>
       </c>
       <c r="T23" t="n">
+        <v>3.02</v>
+      </c>
+      <c r="U23" t="n">
+        <v>1.4</v>
+      </c>
+      <c r="V23" t="n">
+        <v>1.02</v>
+      </c>
+      <c r="W23" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="X23" t="n">
+        <v>3.47</v>
+      </c>
+      <c r="Y23" t="n">
+        <v>2.04</v>
+      </c>
+      <c r="Z23" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="AA23" t="n">
         <v>3.55</v>
       </c>
-      <c r="U23" t="n">
-        <v>1.25</v>
-      </c>
-      <c r="V23" t="n">
-        <v>1.06</v>
-      </c>
-      <c r="W23" t="n">
-        <v>1.49</v>
-      </c>
-      <c r="X23" t="n">
-        <v>2.47</v>
-      </c>
-      <c r="Y23" t="n">
-        <v>2.5</v>
-      </c>
-      <c r="Z23" t="n">
-        <v>1.5</v>
-      </c>
-      <c r="AA23" t="n">
-        <v>5.41</v>
-      </c>
       <c r="AB23" t="n">
-        <v>1.16</v>
+        <v>1.31</v>
       </c>
       <c r="AC23" t="n">
-        <v>2.25</v>
+        <v>1.87</v>
       </c>
       <c r="AD23" t="n">
-        <v>1.55</v>
+        <v>1.87</v>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>['33', '36', '90+5']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -3445,16 +3445,16 @@
         </is>
       </c>
       <c r="AG23" t="n">
-        <v>1.23</v>
+        <v>1.27</v>
       </c>
       <c r="AH23" t="n">
-        <v>2.2</v>
+        <v>1.18</v>
       </c>
       <c r="AI23" t="n">
-        <v>1.57</v>
+        <v>2.62</v>
       </c>
       <c r="AJ23" t="n">
-        <v>3.1</v>
+        <v>1.67</v>
       </c>
       <c r="AK23" s="3" t="n">
         <v>45835.65625</v>
@@ -3481,25 +3481,25 @@
       </c>
       <c r="E24" t="inlineStr">
         <is>
-          <t>Treaty United</t>
+          <t>Wexford</t>
         </is>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>Finn Harps</t>
+          <t>Kerry</t>
         </is>
       </c>
       <c r="G24" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="H24" t="n">
+        <v>3</v>
+      </c>
+      <c r="I24" t="n">
         <v>1</v>
       </c>
-      <c r="I24" t="n">
-        <v>0</v>
-      </c>
       <c r="J24" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="K24" t="inlineStr">
         <is>
@@ -3507,83 +3507,83 @@
         </is>
       </c>
       <c r="L24" t="n">
-        <v>1.5</v>
+        <v>1.77</v>
       </c>
       <c r="M24" t="n">
-        <v>3.95</v>
+        <v>3.5</v>
       </c>
       <c r="N24" t="n">
-        <v>3.82</v>
+        <v>3.2</v>
       </c>
       <c r="O24" t="n">
-        <v>2.38</v>
+        <v>2.43</v>
       </c>
       <c r="P24" t="n">
         <v>2.3</v>
       </c>
       <c r="Q24" t="n">
-        <v>4.1</v>
+        <v>3.9</v>
       </c>
       <c r="R24" t="n">
-        <v>1.3</v>
+        <v>1.32</v>
       </c>
       <c r="S24" t="n">
         <v>3.05</v>
       </c>
       <c r="T24" t="n">
-        <v>2.48</v>
+        <v>2.65</v>
       </c>
       <c r="U24" t="n">
-        <v>1.47</v>
+        <v>1.48</v>
       </c>
       <c r="V24" t="n">
-        <v>1.04</v>
+        <v>1.02</v>
       </c>
       <c r="W24" t="n">
-        <v>1.2</v>
+        <v>1.24</v>
       </c>
       <c r="X24" t="n">
         <v>3.95</v>
       </c>
       <c r="Y24" t="n">
-        <v>1.68</v>
+        <v>1.75</v>
       </c>
       <c r="Z24" t="n">
-        <v>2.05</v>
+        <v>2.07</v>
       </c>
       <c r="AA24" t="n">
-        <v>2.5</v>
+        <v>2.6</v>
       </c>
       <c r="AB24" t="n">
-        <v>1.4</v>
+        <v>1.42</v>
       </c>
       <c r="AC24" t="n">
-        <v>1.62</v>
+        <v>1.61</v>
       </c>
       <c r="AD24" t="n">
-        <v>2.25</v>
+        <v>2.1</v>
       </c>
       <c r="AE24" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>['22', '52', '80', '82']</t>
         </is>
       </c>
       <c r="AF24" t="inlineStr">
         <is>
-          <t>['75']</t>
+          <t>['6', '44', '39']</t>
         </is>
       </c>
       <c r="AG24" t="n">
-        <v>1.25</v>
+        <v>1.24</v>
       </c>
       <c r="AH24" t="n">
-        <v>1.97</v>
+        <v>1.92</v>
       </c>
       <c r="AI24" t="n">
-        <v>1.46</v>
+        <v>1.53</v>
       </c>
       <c r="AJ24" t="n">
-        <v>2.73</v>
+        <v>2.6</v>
       </c>
       <c r="AK24" s="3" t="n">
         <v>45835.65625</v>
@@ -3610,25 +3610,25 @@
       </c>
       <c r="E25" t="inlineStr">
         <is>
-          <t>Bohemians</t>
+          <t>Derry City</t>
         </is>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Sligo Rovers</t>
+          <t>Drogheda United</t>
         </is>
       </c>
       <c r="G25" t="n">
-        <v>1</v>
+        <v>3</v>
       </c>
       <c r="H25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="I25" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="J25" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="K25" t="inlineStr">
         <is>
@@ -3636,83 +3636,83 @@
         </is>
       </c>
       <c r="L25" t="n">
-        <v>1.33</v>
+        <v>1.6</v>
       </c>
       <c r="M25" t="n">
-        <v>4.93</v>
+        <v>3.1</v>
       </c>
       <c r="N25" t="n">
-        <v>8</v>
+        <v>5.73</v>
       </c>
       <c r="O25" t="n">
-        <v>1.86</v>
+        <v>2.52</v>
       </c>
       <c r="P25" t="n">
-        <v>2.71</v>
+        <v>2.02</v>
       </c>
       <c r="Q25" t="n">
-        <v>5.3</v>
+        <v>6.43</v>
       </c>
       <c r="R25" t="n">
+        <v>1.55</v>
+      </c>
+      <c r="S25" t="n">
+        <v>2.38</v>
+      </c>
+      <c r="T25" t="n">
+        <v>3.55</v>
+      </c>
+      <c r="U25" t="n">
         <v>1.25</v>
       </c>
-      <c r="S25" t="n">
-        <v>3.5</v>
-      </c>
-      <c r="T25" t="n">
-        <v>2.35</v>
-      </c>
-      <c r="U25" t="n">
-        <v>1.6</v>
-      </c>
       <c r="V25" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W25" t="n">
-        <v>1.17</v>
+        <v>1.49</v>
       </c>
       <c r="X25" t="n">
-        <v>4.72</v>
+        <v>2.47</v>
       </c>
       <c r="Y25" t="n">
-        <v>1.64</v>
+        <v>2.5</v>
       </c>
       <c r="Z25" t="n">
-        <v>2.32</v>
+        <v>1.5</v>
       </c>
       <c r="AA25" t="n">
-        <v>2.62</v>
+        <v>5.41</v>
       </c>
       <c r="AB25" t="n">
-        <v>1.52</v>
+        <v>1.16</v>
       </c>
       <c r="AC25" t="n">
-        <v>1.8</v>
+        <v>2.25</v>
       </c>
       <c r="AD25" t="n">
-        <v>1.85</v>
+        <v>1.55</v>
       </c>
       <c r="AE25" t="inlineStr">
         <is>
-          <t>['90+5']</t>
+          <t>['33', '36', '90+5']</t>
         </is>
       </c>
       <c r="AF25" t="inlineStr">
         <is>
-          <t>['28']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG25" t="n">
-        <v>1.13</v>
+        <v>1.23</v>
       </c>
       <c r="AH25" t="n">
-        <v>3.3</v>
+        <v>2.2</v>
       </c>
       <c r="AI25" t="n">
-        <v>1.4</v>
+        <v>1.57</v>
       </c>
       <c r="AJ25" t="n">
-        <v>3.3</v>
+        <v>3.1</v>
       </c>
       <c r="AK25" s="3" t="n">
         <v>45835.65625</v>
@@ -3739,25 +3739,25 @@
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>Wexford</t>
+          <t>Dundalk</t>
         </is>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Kerry</t>
+          <t>Cobh Ramblers</t>
         </is>
       </c>
       <c r="G26" t="n">
-        <v>4</v>
+        <v>1</v>
       </c>
       <c r="H26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="I26" t="n">
         <v>1</v>
       </c>
       <c r="J26" t="n">
-        <v>3</v>
+        <v>0</v>
       </c>
       <c r="K26" t="inlineStr">
         <is>
@@ -3765,83 +3765,83 @@
         </is>
       </c>
       <c r="L26" t="n">
-        <v>1.77</v>
+        <v>2.2</v>
       </c>
       <c r="M26" t="n">
-        <v>3.5</v>
+        <v>3.15</v>
       </c>
       <c r="N26" t="n">
-        <v>3.2</v>
+        <v>3.1</v>
       </c>
       <c r="O26" t="n">
-        <v>2.43</v>
+        <v>2.75</v>
       </c>
       <c r="P26" t="n">
-        <v>2.3</v>
+        <v>2.11</v>
       </c>
       <c r="Q26" t="n">
         <v>3.9</v>
       </c>
       <c r="R26" t="n">
-        <v>1.32</v>
+        <v>1.36</v>
       </c>
       <c r="S26" t="n">
-        <v>3.05</v>
+        <v>2.8</v>
       </c>
       <c r="T26" t="n">
-        <v>2.65</v>
+        <v>2.8</v>
       </c>
       <c r="U26" t="n">
-        <v>1.48</v>
+        <v>1.37</v>
       </c>
       <c r="V26" t="n">
-        <v>1.02</v>
+        <v>1.06</v>
       </c>
       <c r="W26" t="n">
-        <v>1.24</v>
+        <v>1.31</v>
       </c>
       <c r="X26" t="n">
-        <v>3.95</v>
+        <v>3.35</v>
       </c>
       <c r="Y26" t="n">
-        <v>1.75</v>
+        <v>2.12</v>
       </c>
       <c r="Z26" t="n">
-        <v>2.07</v>
+        <v>1.74</v>
       </c>
       <c r="AA26" t="n">
-        <v>2.6</v>
+        <v>3.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>1.42</v>
+        <v>1.25</v>
       </c>
       <c r="AC26" t="n">
-        <v>1.61</v>
+        <v>1.81</v>
       </c>
       <c r="AD26" t="n">
-        <v>2.1</v>
+        <v>1.93</v>
       </c>
       <c r="AE26" t="inlineStr">
         <is>
-          <t>['22', '52', '80', '82']</t>
+          <t>['13']</t>
         </is>
       </c>
       <c r="AF26" t="inlineStr">
         <is>
-          <t>['6', '44', '39']</t>
+          <t>[]</t>
         </is>
       </c>
       <c r="AG26" t="n">
-        <v>1.24</v>
+        <v>1.37</v>
       </c>
       <c r="AH26" t="n">
-        <v>1.92</v>
+        <v>1.68</v>
       </c>
       <c r="AI26" t="n">
-        <v>1.53</v>
+        <v>1.62</v>
       </c>
       <c r="AJ26" t="n">
-        <v>2.6</v>
+        <v>2.62</v>
       </c>
       <c r="AK26" s="3" t="n">
         <v>45835.65625</v>
